--- a/backend/tests/api/华泰账单_真实节选_mock.xlsx
+++ b/backend/tests/api/华泰账单_真实节选_mock.xlsx
@@ -852,7 +852,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>27196.66</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>101.05</t>
+          <t>49705.98</t>
         </is>
       </c>
     </row>
